--- a/Results/charts/stats.xlsx
+++ b/Results/charts/stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\progetti_uni\sistemi_architetture_bd\proj_stream\Results\charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778BB6C2-D04E-46F9-B023-24316AEA7270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B22E30-444E-4ADA-B29F-1BC4D9263AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C00845A1-E4B8-49E1-B98B-5AC65EED64DF}"/>
   </bookViews>
@@ -1051,26 +1051,66 @@
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
+      <c r="B12" s="7">
+        <v>2730</v>
+      </c>
+      <c r="C12" s="8">
+        <v>646</v>
+      </c>
+      <c r="D12" s="8">
+        <v>92.1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="F12" s="8">
+        <v>12</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="H12" s="8">
+        <v>54.4</v>
+      </c>
+      <c r="I12" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="J12" s="8">
+        <v>26.1</v>
+      </c>
+      <c r="K12" s="9">
+        <v>5.87</v>
+      </c>
+      <c r="L12" s="7">
+        <v>2950</v>
+      </c>
+      <c r="M12" s="8">
+        <v>243</v>
+      </c>
+      <c r="N12" s="8">
+        <v>99.6</v>
+      </c>
+      <c r="O12" s="8">
+        <v>6.61</v>
+      </c>
+      <c r="P12" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="R12" s="8">
+        <v>58.7</v>
+      </c>
+      <c r="S12" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T12" s="8">
+        <v>28</v>
+      </c>
+      <c r="U12" s="8">
+        <v>2.0099999999999998</v>
+      </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1254,26 +1294,66 @@
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
+      <c r="B17" s="7">
+        <v>2780</v>
+      </c>
+      <c r="C17" s="8">
+        <v>596</v>
+      </c>
+      <c r="D17" s="8">
+        <v>94.5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>20.3</v>
+      </c>
+      <c r="F17" s="8">
+        <v>12.2</v>
+      </c>
+      <c r="G17" s="8">
+        <v>2.48</v>
+      </c>
+      <c r="H17" s="8">
+        <v>56</v>
+      </c>
+      <c r="I17" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="J17" s="8">
+        <v>26.2</v>
+      </c>
+      <c r="K17" s="9">
+        <v>5.94</v>
+      </c>
+      <c r="L17" s="7">
+        <v>2980</v>
+      </c>
+      <c r="M17" s="8">
+        <v>160</v>
+      </c>
+      <c r="N17" s="8">
+        <v>102</v>
+      </c>
+      <c r="O17" s="8">
+        <v>2.73</v>
+      </c>
+      <c r="P17" s="8">
+        <v>13.1</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0.128</v>
+      </c>
+      <c r="R17" s="8">
+        <v>60.2</v>
+      </c>
+      <c r="S17" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="T17" s="8">
+        <v>28.3</v>
+      </c>
+      <c r="U17" s="8">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>

--- a/Results/charts/stats.xlsx
+++ b/Results/charts/stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\progetti_uni\sistemi_architetture_bd\proj_stream\Results\charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B22E30-444E-4ADA-B29F-1BC4D9263AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0A5B92-A8F8-4E69-909D-3F5AA5EA01AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C00845A1-E4B8-49E1-B98B-5AC65EED64DF}"/>
   </bookViews>
@@ -552,6 +552,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -913,51 +914,131 @@
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
+      <c r="B8" s="7">
+        <v>2730</v>
+      </c>
+      <c r="C8" s="8">
+        <v>609</v>
+      </c>
+      <c r="D8" s="8">
+        <v>91.7</v>
+      </c>
+      <c r="E8" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="F8" s="8">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2.59</v>
+      </c>
+      <c r="H8" s="8">
+        <v>53.9</v>
+      </c>
+      <c r="I8" s="8">
+        <v>12</v>
+      </c>
+      <c r="J8" s="8">
+        <v>26.1</v>
+      </c>
+      <c r="K8" s="9">
+        <v>5.52</v>
+      </c>
+      <c r="L8" s="7">
+        <v>2940</v>
+      </c>
+      <c r="M8" s="8">
+        <v>167</v>
+      </c>
+      <c r="N8" s="8">
+        <v>98.8</v>
+      </c>
+      <c r="O8" s="8">
+        <v>2.96</v>
+      </c>
+      <c r="P8" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0.151</v>
+      </c>
+      <c r="R8" s="8">
+        <v>58</v>
+      </c>
+      <c r="S8" s="8">
+        <v>2.48</v>
+      </c>
+      <c r="T8" s="8">
+        <v>27.9</v>
+      </c>
+      <c r="U8" s="8">
+        <v>1.63</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
+      <c r="B9" s="7">
+        <v>2750</v>
+      </c>
+      <c r="C9" s="8">
+        <v>656</v>
+      </c>
+      <c r="D9" s="8">
+        <v>92.3</v>
+      </c>
+      <c r="E9" s="8">
+        <v>22.3</v>
+      </c>
+      <c r="F9" s="8">
+        <v>12</v>
+      </c>
+      <c r="G9" s="8">
+        <v>2.79</v>
+      </c>
+      <c r="H9" s="8">
+        <v>54.3</v>
+      </c>
+      <c r="I9" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="J9" s="8">
+        <v>26.6</v>
+      </c>
+      <c r="K9" s="9">
+        <v>5.44</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2980</v>
+      </c>
+      <c r="M9" s="8">
+        <v>173</v>
+      </c>
+      <c r="N9" s="8">
+        <v>100</v>
+      </c>
+      <c r="O9" s="8">
+        <v>3.14</v>
+      </c>
+      <c r="P9" s="8">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="R9" s="8">
+        <v>58.9</v>
+      </c>
+      <c r="S9" s="8">
+        <v>2.64</v>
+      </c>
+      <c r="T9" s="8">
+        <v>28.3</v>
+      </c>
+      <c r="U9" s="8">
+        <v>1.58</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
@@ -1116,26 +1197,66 @@
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
+      <c r="B13" s="7">
+        <v>730</v>
+      </c>
+      <c r="C13" s="8">
+        <v>619</v>
+      </c>
+      <c r="D13" s="8">
+        <v>92.2</v>
+      </c>
+      <c r="E13" s="8">
+        <v>21</v>
+      </c>
+      <c r="F13" s="8">
+        <v>12</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2.64</v>
+      </c>
+      <c r="H13" s="8">
+        <v>54.4</v>
+      </c>
+      <c r="I13" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="J13" s="8">
+        <v>25.9</v>
+      </c>
+      <c r="K13" s="9">
+        <v>5.89</v>
+      </c>
+      <c r="L13" s="7">
+        <v>2940</v>
+      </c>
+      <c r="M13" s="8">
+        <v>165</v>
+      </c>
+      <c r="N13" s="8">
+        <v>99.6</v>
+      </c>
+      <c r="O13" s="8">
+        <v>3.11</v>
+      </c>
+      <c r="P13" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0.124</v>
+      </c>
+      <c r="R13" s="8">
+        <v>58.7</v>
+      </c>
+      <c r="S13" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="T13" s="8">
+        <v>28</v>
+      </c>
+      <c r="U13" s="8">
+        <v>1.39</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>

--- a/Results/charts/stats.xlsx
+++ b/Results/charts/stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\progetti_uni\sistemi_architetture_bd\proj_stream\Results\charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0A5B92-A8F8-4E69-909D-3F5AA5EA01AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C743E4EC-D671-43F3-B782-04C3509DE479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C00845A1-E4B8-49E1-B98B-5AC65EED64DF}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -194,26 +194,26 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -556,1577 +556,1577 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="4" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="11"/>
+      <c r="J2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="12"/>
+      <c r="L2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="11"/>
+      <c r="P2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1" t="s">
+      <c r="S2" s="11"/>
+      <c r="T2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="U2" s="1"/>
+      <c r="U2" s="11"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>306</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="4">
         <v>33.799999999999997</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="4">
         <v>10.3</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="4">
         <v>1.34</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="4">
         <v>0.10299999999999999</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="4">
         <v>6.13</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="4">
         <v>0.52100000000000002</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="4">
         <v>2.95</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="5">
         <v>0.48599999999999999</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="3">
         <v>308</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="4">
         <v>23.6</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="4">
         <v>10.5</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="4">
         <v>0.625</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="4">
         <v>1.35</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="4">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="4">
         <v>6.18</v>
       </c>
-      <c r="S3" s="8">
+      <c r="S3" s="4">
         <v>0.32600000000000001</v>
       </c>
-      <c r="T3" s="8">
+      <c r="T3" s="4">
         <v>2.95</v>
       </c>
-      <c r="U3" s="8">
+      <c r="U3" s="4">
         <v>0.48399999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>305</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="4">
         <v>34.700000000000003</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="4">
         <v>10.4</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="4">
         <v>1.19</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="4">
         <v>1.34</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="4">
         <v>0.107</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="4">
         <v>6.17</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="4">
         <v>0.63</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="4">
         <v>2.94</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="5">
         <v>0.47599999999999998</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="3">
         <v>308</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="4">
         <v>23.7</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="4">
         <v>10.5</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="4">
         <v>0.67100000000000004</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="4">
         <v>1.35</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="4">
         <v>2.7699999999999999E-2</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="4">
         <v>6.22</v>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="4">
         <v>0.40200000000000002</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="4">
         <v>2.94</v>
       </c>
-      <c r="U4" s="8">
+      <c r="U4" s="4">
         <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>205</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>36.5</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="4">
         <v>10.5</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="4">
         <v>1.34</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="4">
         <v>0.10299999999999999</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="4">
         <v>6.27</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="4">
         <v>0.59</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="4">
         <v>2.93</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="5">
         <v>0.47799999999999998</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="3">
         <v>309</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="4">
         <v>23.7</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="4">
         <v>10.6</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="4">
         <v>0.65800000000000003</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="4">
         <v>1.35</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="4">
         <v>2.07E-2</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="4">
         <v>6.33</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="4">
         <v>0.39800000000000002</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="4">
         <v>2.93</v>
       </c>
-      <c r="U5" s="8">
+      <c r="U5" s="4">
         <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>2730</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>688</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="4">
         <v>91.4</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="4">
         <v>23.3</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="4">
         <v>11.9</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="4">
         <v>2.94</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="4">
         <v>54.5</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="4">
         <v>12.3</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="4">
         <v>26.3</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="5">
         <v>5.78</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="3">
         <v>2970</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="4">
         <v>168</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="4">
         <v>100</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="4">
         <v>3</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="4">
         <v>13</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="4">
         <v>58.8</v>
       </c>
-      <c r="S7" s="8">
+      <c r="S7" s="4">
         <v>2.59</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="4">
         <v>28.3</v>
       </c>
-      <c r="U7" s="8">
+      <c r="U7" s="4">
         <v>1.6</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>2730</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <v>609</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="4">
         <v>91.7</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="4">
         <v>20.6</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="4">
         <v>12</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="4">
         <v>2.59</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="4">
         <v>53.9</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="4">
         <v>12</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="4">
         <v>26.1</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
         <v>5.52</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="3">
         <v>2940</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="4">
         <v>167</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="4">
         <v>98.8</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="4">
         <v>2.96</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="4">
         <v>12.9</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="4">
         <v>0.151</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="4">
         <v>58</v>
       </c>
-      <c r="S8" s="8">
+      <c r="S8" s="4">
         <v>2.48</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="4">
         <v>27.9</v>
       </c>
-      <c r="U8" s="8">
+      <c r="U8" s="4">
         <v>1.63</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="3">
         <v>2750</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="4">
         <v>656</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="4">
         <v>92.3</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="4">
         <v>22.3</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="4">
         <v>12</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="4">
         <v>2.79</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="4">
         <v>54.3</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="4">
         <v>12.9</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="4">
         <v>26.6</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="5">
         <v>5.44</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="3">
         <v>2980</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="4">
         <v>173</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="4">
         <v>100</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="4">
         <v>3.14</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="4">
         <v>13</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="4">
         <v>0.14499999999999999</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="4">
         <v>58.9</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="4">
         <v>2.64</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="4">
         <v>28.3</v>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="4">
         <v>1.58</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>2760</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="4">
         <v>646</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="4">
         <v>93.2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="4">
         <v>22.1</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="4">
         <v>12.1</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="4">
         <v>2.77</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="4">
         <v>55</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="4">
         <v>13</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="4">
         <v>26.4</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="5">
         <v>5.85</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="3">
         <v>2990</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="4">
         <v>173</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="4">
         <v>101</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="4">
         <v>3.2</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="4">
         <v>13.1</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="4">
         <v>0.14599999999999999</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="4">
         <v>59.6</v>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="4">
         <v>2.83</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="4">
         <v>28.5</v>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="4">
         <v>1.17</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <v>2730</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="4">
         <v>646</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="4">
         <v>92.1</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="4">
         <v>21.9</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="4">
         <v>12</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="4">
         <v>2.75</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="4">
         <v>54.4</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="4">
         <v>12.8</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="4">
         <v>26.1</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="5">
         <v>5.87</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="3">
         <v>2950</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="4">
         <v>243</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="4">
         <v>99.6</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="4">
         <v>6.61</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="4">
         <v>12.9</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="4">
         <v>0.61199999999999999</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="4">
         <v>58.7</v>
       </c>
-      <c r="S12" s="8">
+      <c r="S12" s="4">
         <v>4.5999999999999996</v>
       </c>
-      <c r="T12" s="8">
+      <c r="T12" s="4">
         <v>28</v>
       </c>
-      <c r="U12" s="8">
+      <c r="U12" s="4">
         <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
-        <v>730</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="3">
+        <v>2730</v>
+      </c>
+      <c r="C13" s="4">
         <v>619</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="4">
         <v>92.2</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="4">
         <v>21</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="4">
         <v>12</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="4">
         <v>2.64</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="4">
         <v>54.4</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="4">
         <v>12.4</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="4">
         <v>25.9</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="5">
         <v>5.89</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="3">
         <v>2940</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="4">
         <v>165</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="4">
         <v>99.6</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="4">
         <v>3.11</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="4">
         <v>12.9</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13" s="4">
         <v>0.124</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="4">
         <v>58.7</v>
       </c>
-      <c r="S13" s="8">
+      <c r="S13" s="4">
         <v>2.75</v>
       </c>
-      <c r="T13" s="8">
+      <c r="T13" s="4">
         <v>28</v>
       </c>
-      <c r="U13" s="8">
+      <c r="U13" s="4">
         <v>1.39</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="3">
         <v>2760</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="4">
         <v>667</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="4">
         <v>93.7</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="4">
         <v>23</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="4">
         <v>12</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="4">
         <v>2.89</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="4">
         <v>56</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="4">
         <v>12.9</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="4">
         <v>26.3</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="5">
         <v>6.03</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="3">
         <v>2970</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="4">
         <v>242</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="4">
         <v>101</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="4">
         <v>7.2</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="4">
         <v>13.1</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="4">
         <v>0.156</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="4">
         <v>60.1</v>
       </c>
-      <c r="S15" s="8">
+      <c r="S15" s="4">
         <v>4.5599999999999996</v>
       </c>
-      <c r="T15" s="8">
+      <c r="T15" s="4">
         <v>28.3</v>
       </c>
-      <c r="U15" s="8">
+      <c r="U15" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>2760</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="4">
         <v>657</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="4">
         <v>93.7</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="4">
         <v>22.5</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="4">
         <v>12.1</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="4">
         <v>2.83</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="4">
         <v>55.6</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="4">
         <v>13.3</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="4">
         <v>26.4</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="5">
         <v>5.98</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="3">
         <v>2990</v>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="4">
         <v>174</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="4">
         <v>102</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="4">
         <v>3.08</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="4">
         <v>13.1</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q16" s="4">
         <v>0.14299999999999999</v>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="4">
         <v>60.3</v>
       </c>
-      <c r="S16" s="8">
+      <c r="S16" s="4">
         <v>2.72</v>
       </c>
-      <c r="T16" s="8">
+      <c r="T16" s="4">
         <v>28.4</v>
       </c>
-      <c r="U16" s="8">
+      <c r="U16" s="4">
         <v>1.28</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="3">
         <v>2780</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="4">
         <v>596</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="4">
         <v>94.5</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="4">
         <v>20.3</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="4">
         <v>12.2</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="4">
         <v>2.48</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="4">
         <v>56</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="4">
         <v>12.1</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="4">
         <v>26.2</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="5">
         <v>5.94</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="3">
         <v>2980</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="4">
         <v>160</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="4">
         <v>102</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="4">
         <v>2.73</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="4">
         <v>13.1</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17" s="4">
         <v>0.128</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="4">
         <v>60.2</v>
       </c>
-      <c r="S17" s="8">
+      <c r="S17" s="4">
         <v>2.4</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T17" s="4">
         <v>28.3</v>
       </c>
-      <c r="U17" s="8">
+      <c r="U17" s="4">
         <v>1.28</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="3">
         <v>7000</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="4">
         <v>2580</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="4">
         <v>193</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="4">
         <v>71.2</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="4">
         <v>30.6</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="4">
         <v>11.1</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="4">
         <v>96.2</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="4">
         <v>35.6</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="4">
         <v>65.900000000000006</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="5">
         <v>24.7</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="3">
         <v>8540</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="4">
         <v>494</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="4">
         <v>236</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="4">
         <v>7.7</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="4">
         <v>37.299999999999997</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="4">
         <v>0.81200000000000006</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="4">
         <v>118</v>
       </c>
-      <c r="S19" s="8">
+      <c r="S19" s="4">
         <v>5.41</v>
       </c>
-      <c r="T19" s="8">
+      <c r="T19" s="4">
         <v>80.900000000000006</v>
       </c>
-      <c r="U19" s="8">
+      <c r="U19" s="4">
         <v>2.44</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>6820</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="4">
         <v>2670</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="4">
         <v>189</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="4">
         <v>74.5</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="4">
         <v>29.9</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="4">
         <v>11.6</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="4">
         <v>94.1</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="4">
         <v>37.1</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="4">
         <v>66.599999999999994</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="5">
         <v>23.6</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="3">
         <v>8540</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="4">
         <v>452</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="4">
         <v>237</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="4">
         <v>5.91</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="4">
         <v>37.299999999999997</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="Q20" s="4">
         <v>0.28599999999999998</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="4">
         <v>118</v>
       </c>
-      <c r="S20" s="8">
+      <c r="S20" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="T20" s="8">
+      <c r="T20" s="4">
         <v>81.400000000000006</v>
       </c>
-      <c r="U20" s="8">
+      <c r="U20" s="4">
         <v>1.52</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <v>7000</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="4">
         <v>2570</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="4">
         <v>193</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="4">
         <v>71.5</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="4">
         <v>30.6</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="4">
         <v>11.1</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="4">
         <v>96.4</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="4">
         <v>35.6</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="4">
         <v>68.099999999999994</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="4">
         <v>22.4</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="3">
         <v>8560</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="4">
         <v>456</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="4">
         <v>236</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O21" s="4">
         <v>7.94</v>
       </c>
-      <c r="P21" s="8">
+      <c r="P21" s="4">
         <v>37.299999999999997</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="4">
         <v>1.08</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="4">
         <v>118</v>
       </c>
-      <c r="S21" s="8">
+      <c r="S21" s="4">
         <v>5.28</v>
       </c>
-      <c r="T21" s="8">
+      <c r="T21" s="4">
         <v>80.900000000000006</v>
       </c>
-      <c r="U21" s="8">
+      <c r="U21" s="4">
         <v>2.87</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>6860</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="4">
         <v>2700</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="4">
         <v>197</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="4">
         <v>75.599999999999994</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="4">
         <v>30</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="4">
         <v>11.6</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="4">
         <v>103</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="4">
         <v>38.6</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="4">
         <v>65.7</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="5">
         <v>24.7</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="3">
         <v>8550</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="4">
         <v>426</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="4">
         <v>244</v>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="4">
         <v>9.35</v>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="4">
         <v>37.200000000000003</v>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="4">
         <v>0.84599999999999997</v>
       </c>
-      <c r="R23" s="8">
+      <c r="R23" s="4">
         <v>126</v>
       </c>
-      <c r="S23" s="8">
+      <c r="S23" s="4">
         <v>8.4499999999999993</v>
       </c>
-      <c r="T23" s="8">
+      <c r="T23" s="4">
         <v>80.8</v>
       </c>
-      <c r="U23" s="8">
+      <c r="U23" s="4">
         <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>6790</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="4">
         <v>2760</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="4">
         <v>203</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="4">
         <v>82.7</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="4">
         <v>29.7</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="4">
         <v>11.9</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="4">
         <v>110</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="4">
         <v>44.1</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="4">
         <v>68</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="5">
         <v>22</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="3">
         <v>8560</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="4">
         <v>408</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="4">
         <v>256</v>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="4">
         <v>5.03</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="4">
         <v>37.200000000000003</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="Q24" s="4">
         <v>0.26600000000000001</v>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="4">
         <v>137</v>
       </c>
-      <c r="S24" s="8">
+      <c r="S24" s="4">
         <v>4.55</v>
       </c>
-      <c r="T24" s="8">
+      <c r="T24" s="4">
         <v>81</v>
       </c>
-      <c r="U24" s="8">
+      <c r="U24" s="4">
         <v>1.36</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>6720</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="4">
         <v>2800</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="4">
         <v>194</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="4">
         <v>77.2</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="4">
         <v>30</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="4">
         <v>11.5</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="4">
         <v>100</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="4">
         <v>40.4</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="4">
         <v>66.400000000000006</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="5">
         <v>23.4</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="3">
         <v>8390</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="4">
         <v>1010</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="4">
         <v>240</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="4">
         <v>27.1</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="4">
         <v>36.700000000000003</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="4">
         <v>3.16</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="4">
         <v>124</v>
       </c>
-      <c r="S25" s="8">
+      <c r="S25" s="4">
         <v>16.600000000000001</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="4">
         <v>79.5</v>
       </c>
-      <c r="U25" s="8">
+      <c r="U25" s="4">
         <v>8.42</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="3">
         <v>6850</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="4">
         <v>2540</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="4">
         <v>223</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="4">
         <v>88.9</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="4">
         <v>29.6</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="4">
         <v>11.6</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="4">
         <v>129</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="4">
         <v>51.9</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="4">
         <v>64.7</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="5">
         <v>24.5</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="3">
         <v>8380</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="4">
         <v>631</v>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="4">
         <v>278</v>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="4">
         <v>14.3</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="4">
         <v>36.9</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="4">
         <v>0.38400000000000001</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="4">
         <v>161</v>
       </c>
-      <c r="S27" s="8">
+      <c r="S27" s="4">
         <v>11.8</v>
       </c>
-      <c r="T27" s="8">
+      <c r="T27" s="4">
         <v>79.599999999999994</v>
       </c>
-      <c r="U27" s="8">
+      <c r="U27" s="4">
         <v>2.96</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="3">
         <v>6640</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="4">
         <v>2860</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="4">
         <v>222</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="4">
         <v>97.8</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="4">
         <v>29.5</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="4">
         <v>12.1</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="4">
         <v>130</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="4">
         <v>57.6</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="4">
         <v>65.5</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="5">
         <v>24.8</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="3">
         <v>8550</v>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="4">
         <v>420</v>
       </c>
-      <c r="N28" s="8">
+      <c r="N28" s="4">
         <v>288</v>
       </c>
-      <c r="O28" s="8">
+      <c r="O28" s="4">
         <v>5.4</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="4">
         <v>37.4</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="4">
         <v>0.317</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="4">
         <v>169</v>
       </c>
-      <c r="S28" s="8">
+      <c r="S28" s="4">
         <v>5.18</v>
       </c>
-      <c r="T28" s="8">
+      <c r="T28" s="4">
         <v>81.2</v>
       </c>
-      <c r="U28" s="8">
+      <c r="U28" s="4">
         <v>1.19</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="3">
         <v>6800</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="4">
         <v>2730</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="4">
         <v>225</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="4">
         <v>91.8</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="4">
         <v>29.5</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="4">
         <v>12</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="4">
         <v>131</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="4">
         <v>53.7</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="4">
         <v>66.400000000000006</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="5">
         <v>23.9</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="3">
         <v>8440</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="4">
         <v>1030</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="4">
         <v>280</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="4">
         <v>32.4</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="4">
         <v>37.4</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="4">
         <v>0.32800000000000001</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="4">
         <v>164</v>
       </c>
-      <c r="S29" s="8">
+      <c r="S29" s="4">
         <v>18.899999999999999</v>
       </c>
-      <c r="T29" s="8">
+      <c r="T29" s="4">
         <v>80.099999999999994</v>
       </c>
-      <c r="U29" s="8">
+      <c r="U29" s="4">
         <v>7.85</v>
       </c>
     </row>

--- a/Results/charts/stats.xlsx
+++ b/Results/charts/stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\progetti_uni\sistemi_architetture_bd\proj_stream\Results\charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C743E4EC-D671-43F3-B782-04C3509DE479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A00F16-31AA-4C1E-B72E-FB27B610AC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C00845A1-E4B8-49E1-B98B-5AC65EED64DF}"/>
   </bookViews>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="3">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="C5" s="4">
         <v>36.5</v>
